--- a/Result/profitability/6173.xlsx
+++ b/Result/profitability/6173.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6975000000000001</v>
+        <v>0.8562500000000002</v>
       </c>
       <c r="N2" t="n">
-        <v>22.68</v>
+        <v>23.60875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.31</v>
       </c>
       <c r="M3" t="n">
-        <v>0.67125</v>
+        <v>0.8187500000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>21.995</v>
+        <v>23.03875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.27</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6287500000000001</v>
+        <v>0.7650000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>20.94875</v>
+        <v>21.76125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.31</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5025000000000001</v>
+        <v>0.6975000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>19.2775</v>
+        <v>19.9325</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.12</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4587500000000001</v>
+        <v>0.535</v>
       </c>
       <c r="N6" t="n">
-        <v>16.70125</v>
+        <v>17.25125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.16</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3312500000000001</v>
+        <v>0.4125000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>15.84125</v>
+        <v>16.095</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.41</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2400000000000001</v>
+        <v>0.3150000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>15.01375</v>
+        <v>15.075</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6173</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1376</v>
+      </c>
+      <c r="D75" t="n">
+        <v>979</v>
+      </c>
+      <c r="E75" t="n">
+        <v>397</v>
+      </c>
+      <c r="F75" t="n">
+        <v>28.84</v>
+      </c>
+      <c r="G75" t="n">
+        <v>306</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>22.26%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>78</v>
+      </c>
+      <c r="J75" t="n">
+        <v>384</v>
+      </c>
+      <c r="K75" t="n">
+        <v>306</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.9200000000000002</v>
+      </c>
+      <c r="N75" t="n">
+        <v>24.535</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.5042016806722691</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.4899999999999984</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.01728395061728394</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>6.782608695652174</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>5.239999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2220338983050847</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
